--- a/enquiries.xlsx
+++ b/enquiries.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,30 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Parent Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>School Name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
@@ -454,27 +464,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vijay</t>
+          <t>rrgrgrgrgrg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8594684596</t>
+          <t>grgrrgrgr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>grgrgr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>maths</t>
+          <t>grgrgr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>xxxxxx</t>
+          <t>grgrgr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>grgrgr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>grgrgr</t>
         </is>
       </c>
     </row>
